--- a/07-运维服务能力管理内审和管理评审相关制度、计划和报告/word/07-02-07-内审检查表.xlsx
+++ b/07-运维服务能力管理内审和管理评审相关制度、计划和报告/word/07-02-07-内审检查表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19935" windowHeight="7935" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="19935" windowHeight="7935" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="管理要求" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,8 @@
     <sheet name="技术要求" sheetId="4" r:id="rId4"/>
     <sheet name="过程要求" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -125,6 +126,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">制定了运维服务能力管理计划和实施跟踪，有对应的沟通协调机制。
@@ -136,6 +138,7 @@
         <sz val="8"/>
         <color rgb="FFFF0000"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>抽查运维管理部2月与客户进行沟通的记录，发现多次沟通过程没有进行记录。对月度正式运维服务的回顾，并未发现该问题。</t>
@@ -903,13 +906,20 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -917,12 +927,14 @@
       <sz val="8"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -930,31 +942,36 @@
       <sz val="14"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="8"/>
       <color indexed="20"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -962,7 +979,8 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -970,7 +988,8 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -978,6 +997,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -985,13 +1005,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -999,14 +1013,16 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1014,6 +1030,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1022,21 +1039,24 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color indexed="12"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1044,15 +1064,17 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1060,7 +1082,8 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1068,6 +1091,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1075,21 +1099,24 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1097,26 +1124,94 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1128,7 +1223,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1140,163 +1319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1307,169 +1336,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1485,7 +1351,64 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
     </border>
     <border>
       <left/>
@@ -1494,357 +1417,583 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="74">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Percent" xfId="20"/>
+    <cellStyle name="Currency" xfId="21"/>
+    <cellStyle name="Currency [0]" xfId="22"/>
+    <cellStyle name="Comma" xfId="23"/>
+    <cellStyle name="Comma [0]" xfId="24"/>
+    <cellStyle name="Percent" xfId="25"/>
+    <cellStyle name="Currency" xfId="26"/>
+    <cellStyle name="Currency [0]" xfId="27"/>
+    <cellStyle name="Comma" xfId="28"/>
+    <cellStyle name="Comma [0]" xfId="29"/>
+    <cellStyle name="Percent" xfId="30"/>
+    <cellStyle name="Currency" xfId="31"/>
+    <cellStyle name="Currency [0]" xfId="32"/>
+    <cellStyle name="Comma" xfId="33"/>
+    <cellStyle name="Comma [0]" xfId="34"/>
+    <cellStyle name="Percent" xfId="35"/>
+    <cellStyle name="Currency" xfId="36"/>
+    <cellStyle name="Currency [0]" xfId="37"/>
+    <cellStyle name="Comma" xfId="38"/>
+    <cellStyle name="Comma [0]" xfId="39"/>
+    <cellStyle name="货币[0]" xfId="40"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="41"/>
+    <cellStyle name="输入" xfId="42"/>
+    <cellStyle name="货币" xfId="43"/>
+    <cellStyle name="千位分隔[0]" xfId="44"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="45"/>
+    <cellStyle name="差" xfId="46"/>
+    <cellStyle name="千位分隔" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="48"/>
+    <cellStyle name="超链接" xfId="49"/>
+    <cellStyle name="百分比" xfId="50"/>
+    <cellStyle name="已访问的超链接" xfId="51"/>
+    <cellStyle name="注释" xfId="52"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="53"/>
+    <cellStyle name="标题 4" xfId="54"/>
+    <cellStyle name="警告文本" xfId="55"/>
+    <cellStyle name="标题" xfId="56"/>
+    <cellStyle name="解释性文本" xfId="57"/>
+    <cellStyle name="标题 1" xfId="58"/>
+    <cellStyle name="标题 2" xfId="59"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="60"/>
+    <cellStyle name="标题 3" xfId="61"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="62"/>
+    <cellStyle name="输出" xfId="63"/>
+    <cellStyle name="计算" xfId="64"/>
+    <cellStyle name="检查单元格" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="66"/>
+    <cellStyle name="强调文字颜色 2" xfId="67"/>
+    <cellStyle name="链接单元格" xfId="68"/>
+    <cellStyle name="汇总" xfId="69"/>
+    <cellStyle name="好" xfId="70"/>
+    <cellStyle name="适中" xfId="71"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="72"/>
+    <cellStyle name="强调文字颜色 1" xfId="73"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="74"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="75"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="77"/>
+    <cellStyle name="强调文字颜色 3" xfId="78"/>
+    <cellStyle name="强调文字颜色 4" xfId="79"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="80"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="81"/>
+    <cellStyle name="强调文字颜色 5" xfId="82"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="83"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="84"/>
+    <cellStyle name="强调文字颜色 6" xfId="85"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="86"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="87"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2188,25 +2337,27 @@
   <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.63333333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.6333333333333" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.6333333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.6333333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.6333333333333" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="50.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="3" customWidth="1"/>
     <col min="6" max="6" width="7" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11.6333333333333" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="2:5">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="1"/>
       <c r="B1" s="41" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="41"/>
       <c r="D1" s="41"/>
       <c r="E1" s="41"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="20.1" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2216,7 +2367,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2228,7 +2379,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -2248,7 +2399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" ht="94.5" spans="1:13">
+    <row r="5" spans="1:13" ht="94.5">
       <c r="A5" s="39" t="s">
         <v>10</v>
       </c>
@@ -2275,7 +2426,7 @@
       <c r="L5" s="42"/>
       <c r="M5" s="42"/>
     </row>
-    <row r="6" ht="69.95" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" ht="69.95" customHeight="1">
       <c r="A6" s="39"/>
       <c r="B6" s="21" t="s">
         <v>16</v>
@@ -2289,7 +2440,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" ht="69.95" customHeight="1" spans="1:6">
+    <row r="7" spans="1:6" ht="69.95" customHeight="1">
       <c r="A7" s="39"/>
       <c r="B7" s="21" t="s">
         <v>19</v>
@@ -2303,7 +2454,7 @@
       <c r="E7" s="18"/>
       <c r="F7" s="28"/>
     </row>
-    <row r="8" ht="69.95" customHeight="1" spans="1:6">
+    <row r="8" spans="1:6" ht="69.95" customHeight="1">
       <c r="A8" s="39"/>
       <c r="B8" s="21" t="s">
         <v>22</v>
@@ -2317,7 +2468,7 @@
       <c r="E8" s="20"/>
       <c r="F8" s="30"/>
     </row>
-    <row r="9" ht="60" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" ht="60" customHeight="1">
       <c r="A9" s="39" t="s">
         <v>25</v>
       </c>
@@ -2337,7 +2488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" ht="60" customHeight="1">
       <c r="A10" s="39"/>
       <c r="B10" s="15" t="s">
         <v>31</v>
@@ -2351,7 +2502,7 @@
       <c r="E10" s="44"/>
       <c r="F10" s="28"/>
     </row>
-    <row r="11" ht="60" customHeight="1" spans="1:6">
+    <row r="11" spans="1:6" ht="60" customHeight="1">
       <c r="A11" s="39"/>
       <c r="B11" s="15" t="s">
         <v>34</v>
@@ -2365,7 +2516,7 @@
       <c r="E11" s="44"/>
       <c r="F11" s="28"/>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="1:6">
+    <row r="12" spans="1:6" ht="60" customHeight="1">
       <c r="A12" s="39"/>
       <c r="B12" s="15" t="s">
         <v>37</v>
@@ -2379,7 +2530,7 @@
       <c r="E12" s="45"/>
       <c r="F12" s="30"/>
     </row>
-    <row r="13" s="40" customFormat="1" ht="67.5" spans="1:6">
+    <row r="13" spans="1:6" s="40" customFormat="1" ht="67.5">
       <c r="A13" s="14" t="s">
         <v>40</v>
       </c>
@@ -2399,7 +2550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" s="40" customFormat="1" ht="90" customHeight="1" spans="1:6">
+    <row r="14" spans="1:6" s="40" customFormat="1" ht="90" customHeight="1">
       <c r="A14" s="17"/>
       <c r="B14" s="35" t="s">
         <v>45</v>
@@ -2413,7 +2564,7 @@
       <c r="E14" s="18"/>
       <c r="F14" s="31"/>
     </row>
-    <row r="15" s="40" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" s="40" customFormat="1" ht="20.1" customHeight="1">
       <c r="A15" s="19"/>
       <c r="B15" s="35" t="s">
         <v>48</v>
@@ -2427,7 +2578,7 @@
       <c r="E15" s="20"/>
       <c r="F15" s="32"/>
     </row>
-    <row r="16" ht="54" spans="1:6">
+    <row r="16" spans="1:6" ht="54">
       <c r="A16" s="14" t="s">
         <v>51</v>
       </c>
@@ -2447,7 +2598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" ht="69.95" customHeight="1" spans="1:6">
+    <row r="17" spans="1:6" ht="69.95" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="15" t="s">
         <v>56</v>
@@ -2461,7 +2612,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="34"/>
     </row>
-    <row r="18" ht="27" spans="1:6">
+    <row r="18" spans="1:6" ht="27">
       <c r="A18" s="17"/>
       <c r="B18" s="15" t="s">
         <v>59</v>
@@ -2475,7 +2626,7 @@
       <c r="E18" s="21"/>
       <c r="F18" s="34"/>
     </row>
-    <row r="19" ht="60" customHeight="1" spans="1:6">
+    <row r="19" spans="1:6" ht="60" customHeight="1">
       <c r="A19" s="19"/>
       <c r="B19" s="15" t="s">
         <v>62</v>
@@ -2509,8 +2660,7 @@
     <mergeCell ref="F16:F19"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -2523,24 +2673,26 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.63333333333333" style="4" customWidth="1"/>
-    <col min="2" max="2" width="30.6333333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="50.6333333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="20.6333333333333" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.6333333333333" style="37" customWidth="1"/>
+    <col min="1" max="1" width="8.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="30.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="50.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="37" customWidth="1"/>
     <col min="6" max="6" width="7" style="4" customWidth="1"/>
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21" spans="2:5">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="21">
+      <c r="A1" s="1"/>
       <c r="B1" s="6" t="s">
         <v>65</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="20.1" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>66</v>
       </c>
@@ -2550,7 +2702,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2562,7 +2714,7 @@
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -2582,7 +2734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" s="3" customFormat="1" ht="20.1" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>67</v>
       </c>
@@ -2602,7 +2754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A6" s="39"/>
       <c r="B6" s="21" t="s">
         <v>72</v>
@@ -2612,7 +2764,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="31"/>
     </row>
-    <row r="7" s="3" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="7" spans="1:6" s="3" customFormat="1" ht="20.1" customHeight="1">
       <c r="A7" s="39"/>
       <c r="B7" s="21" t="s">
         <v>73</v>
@@ -2624,7 +2776,7 @@
       <c r="E7" s="18"/>
       <c r="F7" s="31"/>
     </row>
-    <row r="8" s="3" customFormat="1" ht="80.1" customHeight="1" spans="1:6">
+    <row r="8" spans="1:6" s="3" customFormat="1" ht="80.1" customHeight="1">
       <c r="A8" s="39"/>
       <c r="B8" s="21" t="s">
         <v>75</v>
@@ -2634,7 +2786,7 @@
       <c r="E8" s="18"/>
       <c r="F8" s="31"/>
     </row>
-    <row r="9" s="3" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" s="3" customFormat="1" ht="20.1" customHeight="1">
       <c r="A9" s="39"/>
       <c r="B9" s="21" t="s">
         <v>76</v>
@@ -2646,7 +2798,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="31"/>
     </row>
-    <row r="10" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A10" s="39"/>
       <c r="B10" s="21" t="s">
         <v>78</v>
@@ -2656,7 +2808,7 @@
       <c r="E10" s="20"/>
       <c r="F10" s="32"/>
     </row>
-    <row r="11" s="3" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="11" spans="1:6" s="3" customFormat="1" ht="20.1" customHeight="1">
       <c r="A11" s="39" t="s">
         <v>79</v>
       </c>
@@ -2676,7 +2828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:6">
+    <row r="12" spans="1:6" ht="20.1" customHeight="1">
       <c r="A12" s="39"/>
       <c r="B12" s="21" t="s">
         <v>84</v>
@@ -2686,7 +2838,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="34"/>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:6">
+    <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="39"/>
       <c r="B13" s="21" t="s">
         <v>85</v>
@@ -2696,7 +2848,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="34"/>
     </row>
-    <row r="14" ht="40.5" spans="1:6">
+    <row r="14" spans="1:6" ht="40.5">
       <c r="A14" s="39"/>
       <c r="B14" s="21" t="s">
         <v>86</v>
@@ -2706,7 +2858,7 @@
       <c r="E14" s="18"/>
       <c r="F14" s="34"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="20.1" customHeight="1">
       <c r="A15" s="39"/>
       <c r="B15" s="21" t="s">
         <v>87</v>
@@ -2716,7 +2868,7 @@
       <c r="E15" s="18"/>
       <c r="F15" s="34"/>
     </row>
-    <row r="16" ht="40.5" spans="1:6">
+    <row r="16" spans="1:6" ht="40.5">
       <c r="A16" s="39"/>
       <c r="B16" s="21" t="s">
         <v>88</v>
@@ -2726,7 +2878,7 @@
       <c r="E16" s="18"/>
       <c r="F16" s="34"/>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:6">
+    <row r="17" spans="1:6" ht="30" customHeight="1">
       <c r="A17" s="39"/>
       <c r="B17" s="21" t="s">
         <v>89</v>
@@ -2736,7 +2888,7 @@
       <c r="E17" s="18"/>
       <c r="F17" s="34"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:6">
+    <row r="18" spans="1:6" ht="20.1" customHeight="1">
       <c r="A18" s="39"/>
       <c r="B18" s="21" t="s">
         <v>90</v>
@@ -2746,7 +2898,7 @@
       <c r="E18" s="18"/>
       <c r="F18" s="34"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:6">
+    <row r="19" spans="1:6" ht="20.1" customHeight="1">
       <c r="A19" s="39"/>
       <c r="B19" s="21" t="s">
         <v>91</v>
@@ -2756,7 +2908,7 @@
       <c r="E19" s="18"/>
       <c r="F19" s="34"/>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="1:6">
+    <row r="20" spans="1:6" ht="30" customHeight="1">
       <c r="A20" s="39"/>
       <c r="B20" s="21" t="s">
         <v>92</v>
@@ -2766,7 +2918,7 @@
       <c r="E20" s="20"/>
       <c r="F20" s="34"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="1:6">
+    <row r="21" spans="1:6" ht="20.1" customHeight="1">
       <c r="A21" s="14" t="s">
         <v>93</v>
       </c>
@@ -2786,7 +2938,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="1:6">
+    <row r="22" spans="1:6" ht="20.1" customHeight="1">
       <c r="A22" s="17"/>
       <c r="B22" s="21" t="s">
         <v>98</v>
@@ -2796,7 +2948,7 @@
       <c r="E22" s="21"/>
       <c r="F22" s="34"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="1:6">
+    <row r="23" spans="1:6" ht="20.1" customHeight="1">
       <c r="A23" s="17"/>
       <c r="B23" s="21" t="s">
         <v>99</v>
@@ -2806,7 +2958,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="34"/>
     </row>
-    <row r="24" ht="40.5" spans="1:6">
+    <row r="24" spans="1:6" ht="40.5">
       <c r="A24" s="17"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
@@ -2816,7 +2968,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="34"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="1:6">
+    <row r="25" spans="1:6" ht="20.1" customHeight="1">
       <c r="A25" s="17"/>
       <c r="B25" s="21" t="s">
         <v>101</v>
@@ -2826,7 +2978,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="34"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="1:6">
+    <row r="26" spans="1:6" ht="20.1" customHeight="1">
       <c r="A26" s="19"/>
       <c r="B26" s="21" t="s">
         <v>102</v>
@@ -2836,7 +2988,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="34"/>
     </row>
-    <row r="27" ht="30" customHeight="1" spans="1:6">
+    <row r="27" spans="1:6" ht="30" customHeight="1">
       <c r="A27" s="14" t="s">
         <v>103</v>
       </c>
@@ -2856,7 +3008,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" spans="1:6">
+    <row r="28" spans="1:6" ht="30" customHeight="1">
       <c r="A28" s="17"/>
       <c r="B28" s="21" t="s">
         <v>108</v>
@@ -2866,7 +3018,7 @@
       <c r="E28" s="18"/>
       <c r="F28" s="31"/>
     </row>
-    <row r="29" ht="30" customHeight="1" spans="1:6">
+    <row r="29" spans="1:6" ht="30" customHeight="1">
       <c r="A29" s="19"/>
       <c r="B29" s="21" t="s">
         <v>109</v>
@@ -2876,7 +3028,7 @@
       <c r="E29" s="20"/>
       <c r="F29" s="32"/>
     </row>
-    <row r="30" ht="30" customHeight="1" spans="1:6">
+    <row r="30" spans="1:6" ht="30" customHeight="1">
       <c r="A30" s="14" t="s">
         <v>110</v>
       </c>
@@ -2896,7 +3048,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" spans="1:6">
+    <row r="31" spans="1:6" ht="30" customHeight="1">
       <c r="A31" s="19"/>
       <c r="B31" s="21" t="s">
         <v>115</v>
@@ -2941,8 +3093,7 @@
     <mergeCell ref="F30:F31"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -2955,24 +3106,26 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.63333333333333" style="4" customWidth="1"/>
-    <col min="2" max="2" width="30.6333333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="50.6333333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="20.6333333333333" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.6333333333333" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="30.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="50.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="4" customWidth="1"/>
     <col min="6" max="6" width="7" style="4" customWidth="1"/>
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21" spans="2:5">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="21">
+      <c r="A1" s="1"/>
       <c r="B1" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="20.1" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>117</v>
       </c>
@@ -2982,7 +3135,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2994,7 +3147,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -3014,7 +3167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>118</v>
       </c>
@@ -3034,7 +3187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="21" t="s">
         <v>123</v>
@@ -3044,7 +3197,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="34"/>
     </row>
-    <row r="7" s="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="7" spans="1:6" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="19"/>
       <c r="B7" s="21" t="s">
         <v>124</v>
@@ -3054,7 +3207,7 @@
       <c r="E7" s="20"/>
       <c r="F7" s="34"/>
     </row>
-    <row r="8" s="3" customFormat="1" ht="80.1" customHeight="1" spans="1:6">
+    <row r="8" spans="1:6" s="3" customFormat="1" ht="80.1" customHeight="1">
       <c r="A8" s="14" t="s">
         <v>125</v>
       </c>
@@ -3074,7 +3227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" ht="80.1" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" s="3" customFormat="1" ht="80.1" customHeight="1">
       <c r="A9" s="17"/>
       <c r="B9" s="21" t="s">
         <v>130</v>
@@ -3084,7 +3237,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="28"/>
     </row>
-    <row r="10" s="3" customFormat="1" ht="80.1" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" s="3" customFormat="1" ht="80.1" customHeight="1">
       <c r="A10" s="19"/>
       <c r="B10" s="21" t="s">
         <v>131</v>
@@ -3094,7 +3247,7 @@
       <c r="E10" s="20"/>
       <c r="F10" s="30"/>
     </row>
-    <row r="11" s="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="11" spans="1:6" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A11" s="14" t="s">
         <v>132</v>
       </c>
@@ -3114,7 +3267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="12" spans="1:6" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="21" t="s">
         <v>137</v>
@@ -3124,7 +3277,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="34"/>
     </row>
-    <row r="13" s="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="13" spans="1:6" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A13" s="17"/>
       <c r="B13" s="21" t="s">
         <v>138</v>
@@ -3134,7 +3287,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="34"/>
     </row>
-    <row r="14" s="3" customFormat="1" ht="80.1" customHeight="1" spans="1:6">
+    <row r="14" spans="1:6" s="3" customFormat="1" ht="80.1" customHeight="1">
       <c r="A14" s="19"/>
       <c r="B14" s="21" t="s">
         <v>139</v>
@@ -3144,7 +3297,7 @@
       <c r="E14" s="20"/>
       <c r="F14" s="34"/>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="14" t="s">
         <v>140</v>
       </c>
@@ -3164,7 +3317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:6">
+    <row r="16" spans="1:6" ht="20.1" customHeight="1">
       <c r="A16" s="17"/>
       <c r="B16" s="21" t="s">
         <v>145</v>
@@ -3174,7 +3327,7 @@
       <c r="E16" s="18"/>
       <c r="F16" s="36"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:6">
+    <row r="17" spans="1:6" ht="20.1" customHeight="1">
       <c r="A17" s="17"/>
       <c r="B17" s="21" t="s">
         <v>146</v>
@@ -3184,7 +3337,7 @@
       <c r="E17" s="18"/>
       <c r="F17" s="36"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:6">
+    <row r="18" spans="1:6" ht="20.1" customHeight="1">
       <c r="A18" s="17"/>
       <c r="B18" s="21" t="s">
         <v>147</v>
@@ -3194,7 +3347,7 @@
       <c r="E18" s="18"/>
       <c r="F18" s="36"/>
     </row>
-    <row r="19" ht="60" customHeight="1" spans="1:6">
+    <row r="19" spans="1:6" ht="60" customHeight="1">
       <c r="A19" s="19"/>
       <c r="B19" s="21" t="s">
         <v>148</v>
@@ -3232,8 +3385,7 @@
     <mergeCell ref="F15:F19"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3246,24 +3398,26 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.63333333333333" style="4" customWidth="1"/>
-    <col min="2" max="2" width="30.6333333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="50.6333333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="20.6333333333333" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.6333333333333" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="30.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="50.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="5" customWidth="1"/>
     <col min="6" max="6" width="7" style="4" customWidth="1"/>
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21" spans="2:5">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="21">
+      <c r="A1" s="1"/>
       <c r="B1" s="6" t="s">
         <v>149</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="20.1" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>150</v>
       </c>
@@ -3273,7 +3427,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -3285,7 +3439,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -3305,7 +3459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>151</v>
       </c>
@@ -3325,7 +3479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="21" t="s">
         <v>156</v>
@@ -3335,7 +3489,7 @@
       <c r="E6" s="21"/>
       <c r="F6" s="17"/>
     </row>
-    <row r="7" s="3" customFormat="1" ht="80.1" customHeight="1" spans="1:6">
+    <row r="7" spans="1:6" s="3" customFormat="1" ht="80.1" customHeight="1">
       <c r="A7" s="19"/>
       <c r="B7" s="21" t="s">
         <v>157</v>
@@ -3345,7 +3499,7 @@
       <c r="E7" s="21"/>
       <c r="F7" s="19"/>
     </row>
-    <row r="8" s="3" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="8" spans="1:6" s="3" customFormat="1" ht="20.1" customHeight="1">
       <c r="A8" s="14" t="s">
         <v>158</v>
       </c>
@@ -3365,7 +3519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" ht="99.95" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" s="3" customFormat="1" ht="99.95" customHeight="1">
       <c r="A9" s="19"/>
       <c r="B9" s="21" t="s">
         <v>163</v>
@@ -3375,7 +3529,7 @@
       <c r="E9" s="20"/>
       <c r="F9" s="19"/>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" ht="20.1" customHeight="1">
       <c r="A10" s="14" t="s">
         <v>164</v>
       </c>
@@ -3395,7 +3549,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:6">
+    <row r="11" spans="1:6" ht="20.1" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="21" t="s">
         <v>169</v>
@@ -3405,7 +3559,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="17"/>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="1:6">
+    <row r="12" spans="1:6" ht="60" customHeight="1">
       <c r="A12" s="19"/>
       <c r="B12" s="21" t="s">
         <v>170</v>
@@ -3438,8 +3592,7 @@
     <mergeCell ref="F10:F12"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3452,24 +3605,26 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.63333333333333" style="4" customWidth="1"/>
-    <col min="2" max="2" width="30.6333333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="50.6333333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="15.6333333333333" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.6333333333333" style="5" customWidth="1"/>
-    <col min="6" max="6" width="8.38333333333333" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="30.625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="50.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="8.375" style="5" customWidth="1"/>
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21" spans="2:5">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="21">
+      <c r="A1" s="1"/>
       <c r="B1" s="6" t="s">
         <v>171</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="20.1" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>117</v>
       </c>
@@ -3479,7 +3634,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -3491,7 +3646,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="20.1" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
@@ -3511,7 +3666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>172</v>
       </c>
@@ -3531,7 +3686,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="15" t="s">
         <v>177</v>
@@ -3541,7 +3696,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="17"/>
     </row>
-    <row r="7" s="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="7" spans="1:6" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="17"/>
       <c r="B7" s="15" t="s">
         <v>178</v>
@@ -3551,7 +3706,7 @@
       <c r="E7" s="18"/>
       <c r="F7" s="17"/>
     </row>
-    <row r="8" s="3" customFormat="1" ht="30" customHeight="1" spans="1:6">
+    <row r="8" spans="1:6" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A8" s="19"/>
       <c r="B8" s="15" t="s">
         <v>179</v>
@@ -3561,7 +3716,7 @@
       <c r="E8" s="20"/>
       <c r="F8" s="19"/>
     </row>
-    <row r="9" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>180</v>
       </c>
@@ -3581,7 +3736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A10" s="17"/>
       <c r="B10" s="15" t="s">
         <v>185</v>
@@ -3591,7 +3746,7 @@
       <c r="E10" s="18"/>
       <c r="F10" s="17"/>
     </row>
-    <row r="11" s="3" customFormat="1" ht="60" customHeight="1" spans="1:6">
+    <row r="11" spans="1:6" s="3" customFormat="1" ht="60" customHeight="1">
       <c r="A11" s="19"/>
       <c r="B11" s="15" t="s">
         <v>186</v>
@@ -3601,7 +3756,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
     </row>
-    <row r="12" s="3" customFormat="1" ht="45" customHeight="1" spans="1:6">
+    <row r="12" spans="1:6" s="3" customFormat="1" ht="45" customHeight="1">
       <c r="A12" s="14" t="s">
         <v>187</v>
       </c>
@@ -3621,7 +3776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" ht="45" customHeight="1" spans="1:6">
+    <row r="13" spans="1:6" s="3" customFormat="1" ht="45" customHeight="1">
       <c r="A13" s="17"/>
       <c r="B13" s="15" t="s">
         <v>192</v>
@@ -3631,7 +3786,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="17"/>
     </row>
-    <row r="14" s="3" customFormat="1" ht="45" customHeight="1" spans="1:6">
+    <row r="14" spans="1:6" s="3" customFormat="1" ht="45" customHeight="1">
       <c r="A14" s="17"/>
       <c r="B14" s="15" t="s">
         <v>193</v>
@@ -3641,7 +3796,7 @@
       <c r="E14" s="18"/>
       <c r="F14" s="17"/>
     </row>
-    <row r="15" s="3" customFormat="1" ht="45" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" s="3" customFormat="1" ht="45" customHeight="1">
       <c r="A15" s="17"/>
       <c r="B15" s="15" t="s">
         <v>194</v>
@@ -3651,7 +3806,7 @@
       <c r="E15" s="18"/>
       <c r="F15" s="17"/>
     </row>
-    <row r="16" s="3" customFormat="1" ht="45" customHeight="1" spans="1:6">
+    <row r="16" spans="1:6" s="3" customFormat="1" ht="45" customHeight="1">
       <c r="A16" s="19"/>
       <c r="B16" s="15" t="s">
         <v>195</v>
@@ -3661,7 +3816,7 @@
       <c r="E16" s="20"/>
       <c r="F16" s="19"/>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:6">
+    <row r="17" spans="1:6" ht="60" customHeight="1">
       <c r="A17" s="14" t="s">
         <v>196</v>
       </c>
@@ -3681,7 +3836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" spans="1:6">
+    <row r="18" spans="1:6" ht="60" customHeight="1">
       <c r="A18" s="17"/>
       <c r="B18" s="15" t="s">
         <v>201</v>
@@ -3691,7 +3846,7 @@
       <c r="E18" s="18"/>
       <c r="F18" s="23"/>
     </row>
-    <row r="19" ht="60" customHeight="1" spans="1:6">
+    <row r="19" spans="1:6" ht="60" customHeight="1">
       <c r="A19" s="17"/>
       <c r="B19" s="15" t="s">
         <v>202</v>
@@ -3701,7 +3856,7 @@
       <c r="E19" s="18"/>
       <c r="F19" s="23"/>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:6">
+    <row r="20" spans="1:6" ht="60" customHeight="1">
       <c r="A20" s="19"/>
       <c r="B20" s="15" t="s">
         <v>203</v>
@@ -3711,7 +3866,7 @@
       <c r="E20" s="18"/>
       <c r="F20" s="24"/>
     </row>
-    <row r="21" ht="66" customHeight="1" spans="1:6">
+    <row r="21" spans="1:6" ht="66" customHeight="1">
       <c r="A21" s="14" t="s">
         <v>204</v>
       </c>
@@ -3731,7 +3886,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1" spans="1:6">
+    <row r="22" spans="1:6" ht="45" customHeight="1">
       <c r="A22" s="17"/>
       <c r="B22" s="15" t="s">
         <v>209</v>
@@ -3741,7 +3896,7 @@
       <c r="E22" s="27"/>
       <c r="F22" s="28"/>
     </row>
-    <row r="23" ht="45" customHeight="1" spans="1:6">
+    <row r="23" spans="1:6" ht="45" customHeight="1">
       <c r="A23" s="19"/>
       <c r="B23" s="15" t="s">
         <v>210</v>
@@ -3751,7 +3906,7 @@
       <c r="E23" s="29"/>
       <c r="F23" s="30"/>
     </row>
-    <row r="24" ht="45" customHeight="1" spans="1:6">
+    <row r="24" spans="1:6" ht="45" customHeight="1">
       <c r="A24" s="14" t="s">
         <v>211</v>
       </c>
@@ -3771,7 +3926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" ht="45" customHeight="1" spans="1:6">
+    <row r="25" spans="1:6" ht="45" customHeight="1">
       <c r="A25" s="17"/>
       <c r="B25" s="15" t="s">
         <v>216</v>
@@ -3781,7 +3936,7 @@
       <c r="E25" s="27"/>
       <c r="F25" s="31"/>
     </row>
-    <row r="26" ht="69.95" customHeight="1" spans="1:6">
+    <row r="26" spans="1:6" ht="69.95" customHeight="1">
       <c r="A26" s="19"/>
       <c r="B26" s="15" t="s">
         <v>217</v>
@@ -3791,7 +3946,7 @@
       <c r="E26" s="29"/>
       <c r="F26" s="32"/>
     </row>
-    <row r="27" ht="30" customHeight="1" spans="1:6">
+    <row r="27" spans="1:6" ht="30" customHeight="1">
       <c r="A27" s="14" t="s">
         <v>218</v>
       </c>
@@ -3811,7 +3966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1" spans="1:6">
+    <row r="28" spans="1:6" ht="45" customHeight="1">
       <c r="A28" s="17"/>
       <c r="B28" s="15" t="s">
         <v>223</v>
@@ -3821,7 +3976,7 @@
       <c r="E28" s="33"/>
       <c r="F28" s="31"/>
     </row>
-    <row r="29" ht="45" customHeight="1" spans="1:6">
+    <row r="29" spans="1:6" ht="45" customHeight="1">
       <c r="A29" s="17"/>
       <c r="B29" s="15" t="s">
         <v>224</v>
@@ -3831,7 +3986,7 @@
       <c r="E29" s="33"/>
       <c r="F29" s="31"/>
     </row>
-    <row r="30" ht="30" customHeight="1" spans="1:6">
+    <row r="30" spans="1:6" ht="30" customHeight="1">
       <c r="A30" s="19"/>
       <c r="B30" s="15" t="s">
         <v>225</v>
@@ -3841,7 +3996,7 @@
       <c r="E30" s="33"/>
       <c r="F30" s="32"/>
     </row>
-    <row r="31" ht="80.1" customHeight="1" spans="1:6">
+    <row r="31" spans="1:6" ht="80.1" customHeight="1">
       <c r="A31" s="14" t="s">
         <v>226</v>
       </c>
@@ -3861,7 +4016,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" ht="45" customHeight="1" spans="1:6">
+    <row r="32" spans="1:6" ht="45" customHeight="1">
       <c r="A32" s="19"/>
       <c r="B32" s="15" t="s">
         <v>231</v>
@@ -3919,7 +4074,6 @@
     <mergeCell ref="F31:F32"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9"/>
 </worksheet>
 </file>